--- a/travel/삿포로/2026_삿포로.xlsx
+++ b/travel/삿포로/2026_삿포로.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tool\여행\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\csw\travel\삿포로\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1D929D1-6C0C-41F9-B248-0279FF8557EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C3B55F-26C0-408A-B54B-F91A235A8D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{16BD92D5-DB44-4AB7-83A8-7317C0E10327}"/>
   </bookViews>
@@ -19,7 +19,6 @@
     <sheet name="숙소후보" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,11 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
-  <si>
-    <t>토</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="44">
   <si>
     <t>일</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -57,16 +52,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>화</t>
-  </si>
-  <si>
     <t>오도리 공원 &amp; tv타워 - 에펠탑</t>
   </si>
   <si>
     <t>스스키노 - 최고의 번화가</t>
-  </si>
-  <si>
-    <t>비에이 버스투어 - 천의 호수, 흰수염 폭포</t>
   </si>
   <si>
     <t>오타루</t>
@@ -153,11 +142,85 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>오도리 공원</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>오타루 당일치기 투어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">토 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>환율</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비행기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>총합</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>엔화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>숙소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비에이 투어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스스키노 집합 출발
+09:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>휴게소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>탁신관&amp;자작나무
+비에이 풍경이 보이는 언덕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>점심식사(준페이식당)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>청의호수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흰수염폭포</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사계채의 언덕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스스키노 도착</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오도리 공원 &amp; tv타워</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>점심</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -165,10 +228,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -202,8 +266,42 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -216,8 +314,49 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -252,19 +391,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -350,16 +476,102 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -384,30 +596,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -417,16 +626,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -435,8 +641,82 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="8" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
+    <cellStyle name="쉼표 [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="좋음" xfId="3" builtinId="26"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
@@ -464,15 +744,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>38101</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:colOff>9527</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>150744</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>657225</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>90482</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -488,7 +768,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -502,8 +782,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="723901" y="219075"/>
-          <a:ext cx="4913243" cy="14125575"/>
+          <a:off x="695327" y="447675"/>
+          <a:ext cx="1333498" cy="3833807"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -524,16 +804,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>152401</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>281609</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>642731</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -549,7 +829,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -563,8 +843,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="5638801" y="238125"/>
-          <a:ext cx="4929808" cy="14173200"/>
+          <a:off x="2057401" y="466725"/>
+          <a:ext cx="1328530" cy="3819525"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -585,16 +865,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>9526</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>38775</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>162591</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>201369</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>73758</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -617,8 +897,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10972800" y="209550"/>
-          <a:ext cx="4839375" cy="4772691"/>
+          <a:off x="3333750" y="428626"/>
+          <a:ext cx="3039819" cy="2997932"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -629,16 +909,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>76881</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>181644</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>501530</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -661,8 +941,96 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15773400" y="209550"/>
-          <a:ext cx="4877481" cy="4791744"/>
+          <a:off x="6353175" y="428625"/>
+          <a:ext cx="3063755" cy="3009900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>38101</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>99764</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="그림 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA756E5D-48C9-413B-0537-05F3468B946F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="723901" y="4829175"/>
+          <a:ext cx="6181724" cy="5538539"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>38101</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>57151</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>93745</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="그림 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D73BE19B-FEC7-E8BA-E8A2-1B0D6B82FCBB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7581901" y="4848225"/>
+          <a:ext cx="4133850" cy="5303920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -702,7 +1070,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="695325" y="1476375"/>
+          <a:off x="695325" y="1495425"/>
           <a:ext cx="13536878" cy="8170457"/>
           <a:chOff x="714375" y="1466850"/>
           <a:chExt cx="13279703" cy="8170457"/>
@@ -912,11 +1280,14 @@
               </a:avLst>
             </a:prstGeom>
             <a:solidFill>
-              <a:schemeClr val="bg1"/>
+              <a:schemeClr val="accent6">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
             </a:solidFill>
             <a:ln w="38100">
               <a:solidFill>
-                <a:srgbClr val="FF0000"/>
+                <a:srgbClr val="00B050"/>
               </a:solidFill>
             </a:ln>
           </xdr:spPr>
@@ -1403,26 +1774,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C15861-8ED4-4CDF-A96D-FFBF70C57626}">
-  <dimension ref="B2:H34"/>
+  <dimension ref="B2:H33"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="5.875" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="25.625" customWidth="1"/>
+    <col min="10" max="10" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="42.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>1</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
@@ -1446,148 +1819,164 @@
       <c r="B4" s="6">
         <v>0</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B5" s="6">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B6" s="6">
         <v>8.3333333333333301E-2</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="6">
         <v>0.125</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="7"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B8" s="6">
         <v>0.16666666666666699</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9" s="6">
         <v>0.20833333333333301</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B10" s="6">
         <v>0.25</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B11" s="6">
         <v>0.29166666666666702</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
     </row>
     <row r="12" spans="2:8" ht="33" x14ac:dyDescent="0.3">
       <c r="B12" s="6">
         <v>0.33333333333333298</v>
       </c>
-      <c r="C12" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
+      <c r="C12" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="44" t="s">
+        <v>23</v>
+      </c>
       <c r="F12" s="7"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:8" ht="33" x14ac:dyDescent="0.3">
       <c r="B13" s="6">
         <v>0.375</v>
       </c>
-      <c r="C13" s="24"/>
+      <c r="C13" s="22"/>
       <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
+      <c r="E13" s="45" t="s">
+        <v>34</v>
+      </c>
       <c r="F13" s="7"/>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B14" s="6">
         <v>0.41666666666666702</v>
       </c>
-      <c r="C14" s="24"/>
+      <c r="C14" s="22"/>
       <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
+      <c r="E14" s="44" t="s">
+        <v>35</v>
+      </c>
       <c r="F14" s="7"/>
     </row>
     <row r="15" spans="2:8" ht="33" x14ac:dyDescent="0.3">
       <c r="B15" s="6">
         <v>0.45833333333333298</v>
       </c>
-      <c r="C15" s="23" t="s">
-        <v>9</v>
+      <c r="C15" s="21" t="s">
+        <v>6</v>
       </c>
       <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
+      <c r="E15" s="45" t="s">
+        <v>36</v>
+      </c>
       <c r="F15" s="7"/>
     </row>
     <row r="16" spans="2:8" ht="33" x14ac:dyDescent="0.3">
       <c r="B16" s="6">
         <v>0.5</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="23" t="s">
-        <v>10</v>
+      <c r="C16" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="6">
         <v>0.54166666666666696</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>27</v>
-      </c>
+      <c r="C17" s="7"/>
       <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="24"/>
+      <c r="E17" s="44" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="22"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="6">
         <v>0.58333333333333304</v>
       </c>
-      <c r="C18" s="7"/>
+      <c r="C18" s="7" t="s">
+        <v>42</v>
+      </c>
       <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="24"/>
+      <c r="E18" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="22"/>
     </row>
     <row r="19" spans="2:6" ht="33" x14ac:dyDescent="0.3">
       <c r="B19" s="6">
@@ -1595,9 +1984,11 @@
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="23" t="s">
-        <v>11</v>
+      <c r="E19" s="44" t="s">
+        <v>40</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
@@ -1606,7 +1997,9 @@
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
+      <c r="E20" s="44" t="s">
+        <v>35</v>
+      </c>
       <c r="F20" s="7"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.3">
@@ -1615,7 +2008,7 @@
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
+      <c r="E21" s="44"/>
       <c r="F21" s="7"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.3">
@@ -1623,14 +2016,12 @@
         <v>0.75</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>25</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E22" s="44"/>
       <c r="F22" s="7"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
@@ -1639,7 +2030,7 @@
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
+      <c r="E23" s="44"/>
       <c r="F23" s="7"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.3">
@@ -1648,7 +2039,9 @@
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
+      <c r="E24" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="F24" s="7"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.3">
@@ -1669,7 +2062,7 @@
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="6">
         <v>0.95833333333333304</v>
       </c>
@@ -1678,36 +2071,36 @@
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B28" s="8">
+    <row r="28" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="23">
         <v>1</v>
       </c>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
+      <c r="C28" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="25"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="17"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C34" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C28:E28"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1715,9 +2108,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A5CBA40-6324-4425-8DB4-19F3F2B3A2A0}">
-  <dimension ref="A1"/>
+  <dimension ref="B2:L23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="L23" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1726,9 +2133,489 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50F81FEC-EC99-4209-A065-067C180A3BFC}">
-  <dimension ref="A1"/>
+  <dimension ref="B2:E74"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="22.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.75" customWidth="1"/>
+    <col min="5" max="5" width="12.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B2" s="32"/>
+      <c r="C2" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="31"/>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="33">
+        <v>1</v>
+      </c>
+      <c r="D3" s="33">
+        <v>8.6265999999999998</v>
+      </c>
+      <c r="E3" s="31"/>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B4" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="35">
+        <f>681900*2</f>
+        <v>1363800</v>
+      </c>
+      <c r="D4" s="35"/>
+      <c r="E4" s="36"/>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B5" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="35">
+        <v>472602</v>
+      </c>
+      <c r="D5" s="35"/>
+      <c r="E5" s="36"/>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B6" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="35">
+        <f>57000*2</f>
+        <v>114000</v>
+      </c>
+      <c r="D6" s="35"/>
+      <c r="E6" s="36"/>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B7" s="34"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="36"/>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="37"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="36"/>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="38"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="36"/>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="34"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="36"/>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="38"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="36"/>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B12" s="37"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="36"/>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="34"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="36"/>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B14" s="34"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="36"/>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B15" s="34"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="36"/>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B16" s="34"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="36"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B17" s="34"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="36"/>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B18" s="34"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="36"/>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B19" s="34"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="36"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="34"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="36"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B21" s="34"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="36"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="34"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="36"/>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B23" s="34"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="36"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B24" s="34"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="36"/>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B25" s="34"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="36"/>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B26" s="34"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="36"/>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B27" s="34"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="36"/>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B28" s="34"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="36"/>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B29" s="34"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="36"/>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B30" s="34"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="36"/>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B31" s="34"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="36"/>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B32" s="34"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="36"/>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B33" s="34"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="35"/>
+      <c r="E33" s="36"/>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B34" s="34"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="36"/>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B35" s="34"/>
+      <c r="C35" s="35"/>
+      <c r="D35" s="35"/>
+      <c r="E35" s="36"/>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B36" s="34"/>
+      <c r="C36" s="35"/>
+      <c r="D36" s="35"/>
+      <c r="E36" s="36"/>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B37" s="34"/>
+      <c r="C37" s="35"/>
+      <c r="D37" s="35"/>
+      <c r="E37" s="36"/>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B38" s="34"/>
+      <c r="C38" s="35"/>
+      <c r="D38" s="35"/>
+      <c r="E38" s="36"/>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B39" s="34"/>
+      <c r="C39" s="35"/>
+      <c r="D39" s="35"/>
+      <c r="E39" s="36"/>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B40" s="34"/>
+      <c r="C40" s="35"/>
+      <c r="D40" s="35"/>
+      <c r="E40" s="36"/>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B41" s="34"/>
+      <c r="C41" s="35"/>
+      <c r="D41" s="35"/>
+      <c r="E41" s="36"/>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B42" s="34"/>
+      <c r="C42" s="35"/>
+      <c r="D42" s="35"/>
+      <c r="E42" s="36"/>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B43" s="34"/>
+      <c r="C43" s="35"/>
+      <c r="D43" s="35"/>
+      <c r="E43" s="36"/>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B44" s="34"/>
+      <c r="C44" s="35"/>
+      <c r="D44" s="35"/>
+      <c r="E44" s="36"/>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B45" s="34"/>
+      <c r="C45" s="35"/>
+      <c r="D45" s="35"/>
+      <c r="E45" s="36"/>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B46" s="34"/>
+      <c r="C46" s="35"/>
+      <c r="D46" s="35"/>
+      <c r="E46" s="36"/>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B47" s="34"/>
+      <c r="C47" s="35"/>
+      <c r="D47" s="35"/>
+      <c r="E47" s="36"/>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B48" s="34"/>
+      <c r="C48" s="35"/>
+      <c r="D48" s="35"/>
+      <c r="E48" s="36"/>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B49" s="34"/>
+      <c r="C49" s="35"/>
+      <c r="D49" s="35"/>
+      <c r="E49" s="36"/>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B50" s="34"/>
+      <c r="C50" s="35"/>
+      <c r="D50" s="35"/>
+      <c r="E50" s="36"/>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B51" s="34"/>
+      <c r="C51" s="35"/>
+      <c r="D51" s="35"/>
+      <c r="E51" s="36"/>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B52" s="34"/>
+      <c r="C52" s="35"/>
+      <c r="D52" s="35"/>
+      <c r="E52" s="36"/>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B53" s="34"/>
+      <c r="C53" s="35"/>
+      <c r="D53" s="35"/>
+      <c r="E53" s="36"/>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B54" s="34"/>
+      <c r="C54" s="35"/>
+      <c r="D54" s="35"/>
+      <c r="E54" s="36"/>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B55" s="34"/>
+      <c r="C55" s="35"/>
+      <c r="D55" s="35"/>
+      <c r="E55" s="36"/>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B56" s="34"/>
+      <c r="C56" s="35"/>
+      <c r="D56" s="35"/>
+      <c r="E56" s="36"/>
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B57" s="34"/>
+      <c r="C57" s="35"/>
+      <c r="D57" s="35"/>
+      <c r="E57" s="36"/>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B58" s="34"/>
+      <c r="C58" s="35"/>
+      <c r="D58" s="35"/>
+      <c r="E58" s="36"/>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B59" s="34"/>
+      <c r="C59" s="35"/>
+      <c r="D59" s="35"/>
+      <c r="E59" s="36"/>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B60" s="34"/>
+      <c r="C60" s="35"/>
+      <c r="D60" s="35"/>
+      <c r="E60" s="36"/>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B61" s="34"/>
+      <c r="C61" s="35"/>
+      <c r="D61" s="35"/>
+      <c r="E61" s="36"/>
+    </row>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B62" s="34"/>
+      <c r="C62" s="35"/>
+      <c r="D62" s="35"/>
+      <c r="E62" s="36"/>
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B63" s="34"/>
+      <c r="C63" s="35"/>
+      <c r="D63" s="35"/>
+      <c r="E63" s="36"/>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B64" s="34"/>
+      <c r="C64" s="35"/>
+      <c r="D64" s="35"/>
+      <c r="E64" s="36"/>
+    </row>
+    <row r="65" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B65" s="34"/>
+      <c r="C65" s="35"/>
+      <c r="D65" s="35"/>
+      <c r="E65" s="36"/>
+    </row>
+    <row r="66" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B66" s="34"/>
+      <c r="C66" s="35"/>
+      <c r="D66" s="35"/>
+      <c r="E66" s="36"/>
+    </row>
+    <row r="67" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B67" s="34"/>
+      <c r="C67" s="35"/>
+      <c r="D67" s="35"/>
+      <c r="E67" s="36"/>
+    </row>
+    <row r="68" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B68" s="34"/>
+      <c r="C68" s="35"/>
+      <c r="D68" s="35"/>
+      <c r="E68" s="36"/>
+    </row>
+    <row r="69" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B69" s="34"/>
+      <c r="C69" s="35"/>
+      <c r="D69" s="35"/>
+      <c r="E69" s="36"/>
+    </row>
+    <row r="70" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B70" s="34"/>
+      <c r="C70" s="35"/>
+      <c r="D70" s="35"/>
+      <c r="E70" s="36"/>
+    </row>
+    <row r="71" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B71" s="34"/>
+      <c r="C71" s="35"/>
+      <c r="D71" s="35"/>
+      <c r="E71" s="36"/>
+    </row>
+    <row r="72" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B72" s="34"/>
+      <c r="C72" s="35"/>
+      <c r="D72" s="35"/>
+      <c r="E72" s="36"/>
+    </row>
+    <row r="73" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B73" s="39"/>
+      <c r="C73" s="40"/>
+      <c r="D73" s="40"/>
+      <c r="E73" s="36"/>
+    </row>
+    <row r="74" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="C74" s="42">
+        <f>SUM(C4:C73)*C3</f>
+        <v>1950402</v>
+      </c>
+      <c r="D74" s="42">
+        <f>SUM(D4:D73)*D3</f>
+        <v>0</v>
+      </c>
+      <c r="E74" s="43">
+        <f>SUM(C74:D74)</f>
+        <v>1950402</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1746,87 +2633,87 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B3" s="14">
+        <v>1</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="10">
+        <v>117721</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="21" t="s">
+      <c r="F3" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="14">
+        <v>2</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="10">
+        <v>220751</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="27">
+        <v>3</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="29">
+        <v>190497</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="16">
+        <v>4</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="13">
+        <v>171897</v>
+      </c>
+      <c r="E6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="22" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B3" s="16">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="12">
-        <v>117721</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="16">
-        <v>2</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="12">
-        <v>220751</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="17">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="16">
-        <v>3</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="12">
-        <v>190497</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B6" s="18">
-        <v>4</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="15">
-        <v>171897</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="19">
+      <c r="F6" s="17">
         <v>4</v>
       </c>
     </row>

--- a/travel/삿포로/2026_삿포로.xlsx
+++ b/travel/삿포로/2026_삿포로.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\csw\travel\삿포로\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\csw\travel\삿포로\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C3B55F-26C0-408A-B54B-F91A235A8D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAC4B876-A67E-4334-B919-0F3B5957CF9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{16BD92D5-DB44-4AB7-83A8-7317C0E10327}"/>
+    <workbookView xWindow="28680" yWindow="4500" windowWidth="29040" windowHeight="15720" xr2:uid="{16BD92D5-DB44-4AB7-83A8-7317C0E10327}"/>
   </bookViews>
   <sheets>
     <sheet name="일정" sheetId="2" r:id="rId1"/>
@@ -34,15 +34,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="48">
   <si>
     <t>일</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -196,10 +193,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>점심식사(준페이식당)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>청의호수</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -221,6 +214,37 @@
   </si>
   <si>
     <t>점심</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스스키노 -&gt; 삿포로 역
+(지하철)
+삿포로 역 -&gt; 미나미 오타루
+(JR 열차 자유석)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>점심식사
+(준페이식당)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[시카이마치도리 거리]
+오르골당
+증기 시계
+기타이치 유리 3호관
+르타오 무료전망대
+(치즈케이크)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오타루 운하
+오타루 삼각시장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>점심
+(스시거리 or 삼각시장 - 카이센동)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -596,13 +620,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -644,15 +668,6 @@
     <xf numFmtId="20" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -663,9 +678,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -712,6 +724,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1778,7 +1802,9 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="5.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="25.625" customWidth="1"/>
+    <col min="3" max="3" width="25.625" customWidth="1"/>
+    <col min="4" max="4" width="26.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="25.625" customWidth="1"/>
     <col min="10" max="10" width="15.875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="42.125" bestFit="1" customWidth="1"/>
   </cols>
@@ -1819,73 +1845,73 @@
       <c r="B4" s="6">
         <v>0</v>
       </c>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B5" s="6">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B6" s="6">
         <v>8.3333333333333301E-2</v>
       </c>
-      <c r="C6" s="46"/>
-      <c r="D6" s="46"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="6">
         <v>0.125</v>
       </c>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B8" s="6">
         <v>0.16666666666666699</v>
       </c>
-      <c r="C8" s="46"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="46"/>
-      <c r="F8" s="46"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9" s="6">
         <v>0.20833333333333301</v>
       </c>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B10" s="6">
         <v>0.25</v>
       </c>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B11" s="6">
         <v>0.29166666666666702</v>
       </c>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
     </row>
     <row r="12" spans="2:8" ht="33" x14ac:dyDescent="0.3">
       <c r="B12" s="6">
@@ -1897,29 +1923,33 @@
       <c r="D12" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="44" t="s">
+      <c r="E12" s="40" t="s">
         <v>23</v>
       </c>
       <c r="F12" s="7"/>
     </row>
-    <row r="13" spans="2:8" ht="33" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:8" ht="66" x14ac:dyDescent="0.3">
       <c r="B13" s="6">
         <v>0.375</v>
       </c>
       <c r="C13" s="22"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="45" t="s">
+      <c r="D13" s="46" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="41" t="s">
         <v>34</v>
       </c>
       <c r="F13" s="7"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:8" ht="99" x14ac:dyDescent="0.3">
       <c r="B14" s="6">
         <v>0.41666666666666702</v>
       </c>
       <c r="C14" s="22"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="44" t="s">
+      <c r="D14" s="46" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="40" t="s">
         <v>35</v>
       </c>
       <c r="F14" s="7"/>
@@ -1932,23 +1962,23 @@
         <v>6</v>
       </c>
       <c r="D15" s="7"/>
-      <c r="E15" s="45" t="s">
+      <c r="E15" s="41" t="s">
         <v>36</v>
       </c>
       <c r="F15" s="7"/>
     </row>
-    <row r="16" spans="2:8" ht="33" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:8" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B16" s="6">
         <v>0.5</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="44" t="s">
-        <v>37</v>
+        <v>42</v>
+      </c>
+      <c r="D16" s="46" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="41" t="s">
+        <v>44</v>
       </c>
       <c r="F16" s="21" t="s">
         <v>7</v>
@@ -1960,21 +1990,23 @@
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
-      <c r="E17" s="44" t="s">
-        <v>38</v>
+      <c r="E17" s="40" t="s">
+        <v>37</v>
       </c>
       <c r="F17" s="22"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" ht="33" x14ac:dyDescent="0.3">
       <c r="B18" s="6">
         <v>0.58333333333333304</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="44" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="D18" s="46" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="40" t="s">
+        <v>38</v>
       </c>
       <c r="F18" s="22"/>
     </row>
@@ -1984,8 +2016,8 @@
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
-      <c r="E19" s="44" t="s">
-        <v>40</v>
+      <c r="E19" s="40" t="s">
+        <v>39</v>
       </c>
       <c r="F19" s="21" t="s">
         <v>8</v>
@@ -1997,7 +2029,7 @@
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
-      <c r="E20" s="44" t="s">
+      <c r="E20" s="40" t="s">
         <v>35</v>
       </c>
       <c r="F20" s="7"/>
@@ -2008,7 +2040,7 @@
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
-      <c r="E21" s="44"/>
+      <c r="E21" s="40"/>
       <c r="F21" s="7"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.3">
@@ -2021,7 +2053,7 @@
       <c r="D22" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E22" s="44"/>
+      <c r="E22" s="40"/>
       <c r="F22" s="7"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
@@ -2030,7 +2062,7 @@
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
-      <c r="E23" s="44"/>
+      <c r="E23" s="40"/>
       <c r="F23" s="7"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.3">
@@ -2039,8 +2071,8 @@
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
-      <c r="E24" s="44" t="s">
-        <v>41</v>
+      <c r="E24" s="40" t="s">
+        <v>40</v>
       </c>
       <c r="F24" s="7"/>
     </row>
@@ -2075,11 +2107,11 @@
       <c r="B28" s="23">
         <v>1</v>
       </c>
-      <c r="C28" s="24" t="s">
+      <c r="C28" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="D28" s="25"/>
-      <c r="E28" s="26"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="45"/>
       <c r="F28" s="17"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.3">
@@ -2103,6 +2135,9 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;8&amp;K000000 Internal</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2127,6 +2162,9 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;8&amp;K000000 Internal</oddFooter>
+  </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -2143,474 +2181,474 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B2" s="32"/>
-      <c r="C2" s="32" t="s">
+      <c r="B2" s="28"/>
+      <c r="C2" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="31"/>
+      <c r="E2" s="8"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="33">
+      <c r="C3" s="29">
         <v>1</v>
       </c>
-      <c r="D3" s="33">
+      <c r="D3" s="29">
         <v>8.6265999999999998</v>
       </c>
-      <c r="E3" s="31"/>
+      <c r="E3" s="8"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="35">
+      <c r="C4" s="31">
         <f>681900*2</f>
         <v>1363800</v>
       </c>
-      <c r="D4" s="35"/>
-      <c r="E4" s="36"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="32"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="31">
         <v>472602</v>
       </c>
-      <c r="D5" s="35"/>
-      <c r="E5" s="36"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="32"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="35">
+      <c r="C6" s="31">
         <f>57000*2</f>
         <v>114000</v>
       </c>
-      <c r="D6" s="35"/>
-      <c r="E6" s="36"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="32"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="34"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="36"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="32"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="37"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="36"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="32"/>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="38"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="36"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="32"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="34"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="36"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="32"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="38"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="36"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="32"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="37"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="36"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="32"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="34"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="36"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="32"/>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="34"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="36"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="32"/>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="34"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="36"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="32"/>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="34"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="36"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="32"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="34"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="36"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="32"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B18" s="34"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="36"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="32"/>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B19" s="34"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="36"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="32"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="34"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="36"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="32"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B21" s="34"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="36"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="32"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="34"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="36"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="32"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B23" s="34"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="36"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="32"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B24" s="34"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="36"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="32"/>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B25" s="34"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="36"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="32"/>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B26" s="34"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="36"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="32"/>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B27" s="34"/>
-      <c r="C27" s="35"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="36"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="32"/>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B28" s="34"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="36"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="32"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B29" s="34"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="36"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="32"/>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B30" s="34"/>
-      <c r="C30" s="35"/>
-      <c r="D30" s="35"/>
-      <c r="E30" s="36"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="32"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B31" s="34"/>
-      <c r="C31" s="35"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="36"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="32"/>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B32" s="34"/>
-      <c r="C32" s="35"/>
-      <c r="D32" s="35"/>
-      <c r="E32" s="36"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="32"/>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B33" s="34"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="35"/>
-      <c r="E33" s="36"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="32"/>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B34" s="34"/>
-      <c r="C34" s="35"/>
-      <c r="D34" s="35"/>
-      <c r="E34" s="36"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="32"/>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B35" s="34"/>
-      <c r="C35" s="35"/>
-      <c r="D35" s="35"/>
-      <c r="E35" s="36"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="32"/>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B36" s="34"/>
-      <c r="C36" s="35"/>
-      <c r="D36" s="35"/>
-      <c r="E36" s="36"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="32"/>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B37" s="34"/>
-      <c r="C37" s="35"/>
-      <c r="D37" s="35"/>
-      <c r="E37" s="36"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="32"/>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B38" s="34"/>
-      <c r="C38" s="35"/>
-      <c r="D38" s="35"/>
-      <c r="E38" s="36"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="32"/>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B39" s="34"/>
-      <c r="C39" s="35"/>
-      <c r="D39" s="35"/>
-      <c r="E39" s="36"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="32"/>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B40" s="34"/>
-      <c r="C40" s="35"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="36"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="32"/>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B41" s="34"/>
-      <c r="C41" s="35"/>
-      <c r="D41" s="35"/>
-      <c r="E41" s="36"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="32"/>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B42" s="34"/>
-      <c r="C42" s="35"/>
-      <c r="D42" s="35"/>
-      <c r="E42" s="36"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="31"/>
+      <c r="D42" s="31"/>
+      <c r="E42" s="32"/>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B43" s="34"/>
-      <c r="C43" s="35"/>
-      <c r="D43" s="35"/>
-      <c r="E43" s="36"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="31"/>
+      <c r="E43" s="32"/>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B44" s="34"/>
-      <c r="C44" s="35"/>
-      <c r="D44" s="35"/>
-      <c r="E44" s="36"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="31"/>
+      <c r="D44" s="31"/>
+      <c r="E44" s="32"/>
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B45" s="34"/>
-      <c r="C45" s="35"/>
-      <c r="D45" s="35"/>
-      <c r="E45" s="36"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="32"/>
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B46" s="34"/>
-      <c r="C46" s="35"/>
-      <c r="D46" s="35"/>
-      <c r="E46" s="36"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="31"/>
+      <c r="D46" s="31"/>
+      <c r="E46" s="32"/>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B47" s="34"/>
-      <c r="C47" s="35"/>
-      <c r="D47" s="35"/>
-      <c r="E47" s="36"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="31"/>
+      <c r="E47" s="32"/>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B48" s="34"/>
-      <c r="C48" s="35"/>
-      <c r="D48" s="35"/>
-      <c r="E48" s="36"/>
+      <c r="B48" s="30"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="31"/>
+      <c r="E48" s="32"/>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B49" s="34"/>
-      <c r="C49" s="35"/>
-      <c r="D49" s="35"/>
-      <c r="E49" s="36"/>
+      <c r="B49" s="30"/>
+      <c r="C49" s="31"/>
+      <c r="D49" s="31"/>
+      <c r="E49" s="32"/>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B50" s="34"/>
-      <c r="C50" s="35"/>
-      <c r="D50" s="35"/>
-      <c r="E50" s="36"/>
+      <c r="B50" s="30"/>
+      <c r="C50" s="31"/>
+      <c r="D50" s="31"/>
+      <c r="E50" s="32"/>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B51" s="34"/>
-      <c r="C51" s="35"/>
-      <c r="D51" s="35"/>
-      <c r="E51" s="36"/>
+      <c r="B51" s="30"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="31"/>
+      <c r="E51" s="32"/>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B52" s="34"/>
-      <c r="C52" s="35"/>
-      <c r="D52" s="35"/>
-      <c r="E52" s="36"/>
+      <c r="B52" s="30"/>
+      <c r="C52" s="31"/>
+      <c r="D52" s="31"/>
+      <c r="E52" s="32"/>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B53" s="34"/>
-      <c r="C53" s="35"/>
-      <c r="D53" s="35"/>
-      <c r="E53" s="36"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="31"/>
+      <c r="E53" s="32"/>
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B54" s="34"/>
-      <c r="C54" s="35"/>
-      <c r="D54" s="35"/>
-      <c r="E54" s="36"/>
+      <c r="B54" s="30"/>
+      <c r="C54" s="31"/>
+      <c r="D54" s="31"/>
+      <c r="E54" s="32"/>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B55" s="34"/>
-      <c r="C55" s="35"/>
-      <c r="D55" s="35"/>
-      <c r="E55" s="36"/>
+      <c r="B55" s="30"/>
+      <c r="C55" s="31"/>
+      <c r="D55" s="31"/>
+      <c r="E55" s="32"/>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B56" s="34"/>
-      <c r="C56" s="35"/>
-      <c r="D56" s="35"/>
-      <c r="E56" s="36"/>
+      <c r="B56" s="30"/>
+      <c r="C56" s="31"/>
+      <c r="D56" s="31"/>
+      <c r="E56" s="32"/>
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B57" s="34"/>
-      <c r="C57" s="35"/>
-      <c r="D57" s="35"/>
-      <c r="E57" s="36"/>
+      <c r="B57" s="30"/>
+      <c r="C57" s="31"/>
+      <c r="D57" s="31"/>
+      <c r="E57" s="32"/>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B58" s="34"/>
-      <c r="C58" s="35"/>
-      <c r="D58" s="35"/>
-      <c r="E58" s="36"/>
+      <c r="B58" s="30"/>
+      <c r="C58" s="31"/>
+      <c r="D58" s="31"/>
+      <c r="E58" s="32"/>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B59" s="34"/>
-      <c r="C59" s="35"/>
-      <c r="D59" s="35"/>
-      <c r="E59" s="36"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="31"/>
+      <c r="D59" s="31"/>
+      <c r="E59" s="32"/>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B60" s="34"/>
-      <c r="C60" s="35"/>
-      <c r="D60" s="35"/>
-      <c r="E60" s="36"/>
+      <c r="B60" s="30"/>
+      <c r="C60" s="31"/>
+      <c r="D60" s="31"/>
+      <c r="E60" s="32"/>
     </row>
     <row r="61" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B61" s="34"/>
-      <c r="C61" s="35"/>
-      <c r="D61" s="35"/>
-      <c r="E61" s="36"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="31"/>
+      <c r="D61" s="31"/>
+      <c r="E61" s="32"/>
     </row>
     <row r="62" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B62" s="34"/>
-      <c r="C62" s="35"/>
-      <c r="D62" s="35"/>
-      <c r="E62" s="36"/>
+      <c r="B62" s="30"/>
+      <c r="C62" s="31"/>
+      <c r="D62" s="31"/>
+      <c r="E62" s="32"/>
     </row>
     <row r="63" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B63" s="34"/>
-      <c r="C63" s="35"/>
-      <c r="D63" s="35"/>
-      <c r="E63" s="36"/>
+      <c r="B63" s="30"/>
+      <c r="C63" s="31"/>
+      <c r="D63" s="31"/>
+      <c r="E63" s="32"/>
     </row>
     <row r="64" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B64" s="34"/>
-      <c r="C64" s="35"/>
-      <c r="D64" s="35"/>
-      <c r="E64" s="36"/>
+      <c r="B64" s="30"/>
+      <c r="C64" s="31"/>
+      <c r="D64" s="31"/>
+      <c r="E64" s="32"/>
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B65" s="34"/>
-      <c r="C65" s="35"/>
-      <c r="D65" s="35"/>
-      <c r="E65" s="36"/>
+      <c r="B65" s="30"/>
+      <c r="C65" s="31"/>
+      <c r="D65" s="31"/>
+      <c r="E65" s="32"/>
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B66" s="34"/>
-      <c r="C66" s="35"/>
-      <c r="D66" s="35"/>
-      <c r="E66" s="36"/>
+      <c r="B66" s="30"/>
+      <c r="C66" s="31"/>
+      <c r="D66" s="31"/>
+      <c r="E66" s="32"/>
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B67" s="34"/>
-      <c r="C67" s="35"/>
-      <c r="D67" s="35"/>
-      <c r="E67" s="36"/>
+      <c r="B67" s="30"/>
+      <c r="C67" s="31"/>
+      <c r="D67" s="31"/>
+      <c r="E67" s="32"/>
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B68" s="34"/>
-      <c r="C68" s="35"/>
-      <c r="D68" s="35"/>
-      <c r="E68" s="36"/>
+      <c r="B68" s="30"/>
+      <c r="C68" s="31"/>
+      <c r="D68" s="31"/>
+      <c r="E68" s="32"/>
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B69" s="34"/>
-      <c r="C69" s="35"/>
-      <c r="D69" s="35"/>
-      <c r="E69" s="36"/>
+      <c r="B69" s="30"/>
+      <c r="C69" s="31"/>
+      <c r="D69" s="31"/>
+      <c r="E69" s="32"/>
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B70" s="34"/>
-      <c r="C70" s="35"/>
-      <c r="D70" s="35"/>
-      <c r="E70" s="36"/>
+      <c r="B70" s="30"/>
+      <c r="C70" s="31"/>
+      <c r="D70" s="31"/>
+      <c r="E70" s="32"/>
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B71" s="34"/>
-      <c r="C71" s="35"/>
-      <c r="D71" s="35"/>
-      <c r="E71" s="36"/>
+      <c r="B71" s="30"/>
+      <c r="C71" s="31"/>
+      <c r="D71" s="31"/>
+      <c r="E71" s="32"/>
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B72" s="34"/>
-      <c r="C72" s="35"/>
-      <c r="D72" s="35"/>
-      <c r="E72" s="36"/>
+      <c r="B72" s="30"/>
+      <c r="C72" s="31"/>
+      <c r="D72" s="31"/>
+      <c r="E72" s="32"/>
     </row>
     <row r="73" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="39"/>
-      <c r="C73" s="40"/>
-      <c r="D73" s="40"/>
-      <c r="E73" s="36"/>
+      <c r="B73" s="35"/>
+      <c r="C73" s="36"/>
+      <c r="D73" s="36"/>
+      <c r="E73" s="32"/>
     </row>
     <row r="74" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="41" t="s">
+      <c r="B74" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="C74" s="42">
+      <c r="C74" s="38">
         <f>SUM(C4:C73)*C3</f>
         <v>1950402</v>
       </c>
-      <c r="D74" s="42">
+      <c r="D74" s="38">
         <f>SUM(D4:D73)*D3</f>
         <v>0</v>
       </c>
-      <c r="E74" s="43">
+      <c r="E74" s="39">
         <f>SUM(C74:D74)</f>
         <v>1950402</v>
       </c>
@@ -2618,6 +2656,9 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;8&amp;K000000 Internal</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2684,19 +2725,19 @@
       </c>
     </row>
     <row r="5" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="27">
+      <c r="B5" s="24">
         <v>3</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="26">
         <v>190497</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="27">
         <v>1</v>
       </c>
     </row>
@@ -2726,6 +2767,15 @@
     <hyperlink ref="C6" r:id="rId4" xr:uid="{008F70B1-1F63-445B-AC47-BF60217FFFC7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;8&amp;K000000 Internal</oddFooter>
+  </headerFooter>
   <drawing r:id="rId5"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{7e753c2c-bb14-4786-921b-97c6a6fc424f}" enabled="1" method="Standard" siteId="{3bd97919-57c3-48d3-9e9a-8e4c01614a8f}" contentBits="2" removed="0"/>
+</clbl:labelList>
 </file>
--- a/travel/삿포로/2026_삿포로.xlsx
+++ b/travel/삿포로/2026_삿포로.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\csw\travel\삿포로\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\csw\travel\삿포로\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAC4B876-A67E-4334-B919-0F3B5957CF9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CEFFA96-153A-438F-805C-451FA1E07FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="4500" windowWidth="29040" windowHeight="15720" xr2:uid="{16BD92D5-DB44-4AB7-83A8-7317C0E10327}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{16BD92D5-DB44-4AB7-83A8-7317C0E10327}"/>
   </bookViews>
   <sheets>
     <sheet name="일정" sheetId="2" r:id="rId1"/>
@@ -34,12 +34,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
   <si>
     <t>일</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -131,14 +134,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>저녁 - 스스키노</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>비에이 버스투어</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>오타루 당일치기 투어</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -176,11 +171,6 @@
   </si>
   <si>
     <t>비에이 투어</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스스키노 집합 출발
-09:30</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -205,15 +195,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>스스키노 도착</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>오도리 공원 &amp; tv타워</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>점심</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -224,27 +206,109 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>점심식사
-(준페이식당)</t>
+    <t>비에이 버스투어
+(야놀자)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스스키노 도착
+20:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스스키노 집합 및 출발
+09:20 - 09:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+오타루 삼각시장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오타루 운하</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미나미 오타루 -&gt; 삿포로 역
+(JR 열차 자유석)
+삿포로 역 -&gt; 스스키노
+(지하철)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>청주 공항 도착
+07:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>세종 출발
+06:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기상
+05:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[점심]
+스시거리 or 삼각시장 - 카이센동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[점심]
+라멘 신겐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[점심]
+준페이식당</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[저녁]
+스스키노 징기스칸 유우히</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eSIM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여행자보험</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[저녁]
+카이센동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[아침]
+스프 카레</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[저녁]
+토리돈 스시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>삿포로 맥주박물관
+(마지막 입장 17:30)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쇼핑</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[시카이마치도리 거리]
-오르골당
-증기 시계
+오르골당, 증기 시계+D11
 기타이치 유리 3호관
 르타오 무료전망대
 (치즈케이크)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오타루 운하
-오타루 삼각시장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>점심
-(스시거리 or 삼각시장 - 카이센동)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -256,7 +320,7 @@
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -306,26 +370,8 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <strike/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <strike/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -379,8 +425,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -580,6 +632,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -595,7 +662,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -695,15 +762,6 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -725,6 +783,9 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -734,7 +795,22 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1812,10 +1888,10 @@
     <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>0</v>
@@ -1845,73 +1921,79 @@
       <c r="B4" s="6">
         <v>0</v>
       </c>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B5" s="6">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B6" s="6">
         <v>8.3333333333333301E-2</v>
       </c>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="6">
         <v>0.125</v>
       </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+    </row>
+    <row r="8" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="6">
         <v>0.16666666666666699</v>
       </c>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B9" s="6">
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+    </row>
+    <row r="9" spans="2:8" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="45">
         <v>0.20833333333333301</v>
       </c>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C9" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="46"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+    </row>
+    <row r="10" spans="2:8" ht="33" x14ac:dyDescent="0.3">
       <c r="B10" s="6">
         <v>0.25</v>
       </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C10" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+    </row>
+    <row r="11" spans="2:8" ht="33" x14ac:dyDescent="0.3">
       <c r="B11" s="6">
         <v>0.29166666666666702</v>
       </c>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
+      <c r="C11" s="44" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
     </row>
     <row r="12" spans="2:8" ht="33" x14ac:dyDescent="0.3">
       <c r="B12" s="6">
@@ -1921,10 +2003,10 @@
         <v>5</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="40" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="E12" s="38" t="s">
+        <v>39</v>
       </c>
       <c r="F12" s="7"/>
     </row>
@@ -1933,24 +2015,26 @@
         <v>0.375</v>
       </c>
       <c r="C13" s="22"/>
-      <c r="D13" s="46" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="F13" s="7"/>
-    </row>
-    <row r="14" spans="2:8" ht="99" x14ac:dyDescent="0.3">
+      <c r="D13" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="48" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B14" s="6">
         <v>0.41666666666666702</v>
       </c>
       <c r="C14" s="22"/>
-      <c r="D14" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="40" t="s">
-        <v>35</v>
+      <c r="D14" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="37" t="s">
+        <v>32</v>
       </c>
       <c r="F14" s="7"/>
     </row>
@@ -1961,9 +2045,11 @@
       <c r="C15" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="41" t="s">
-        <v>36</v>
+      <c r="D15" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="38" t="s">
+        <v>33</v>
       </c>
       <c r="F15" s="7"/>
     </row>
@@ -1971,14 +2057,14 @@
       <c r="B16" s="6">
         <v>0.5</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" s="46" t="s">
-        <v>47</v>
-      </c>
-      <c r="E16" s="41" t="s">
-        <v>44</v>
+      <c r="C16" s="48" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="38" t="s">
+        <v>50</v>
       </c>
       <c r="F16" s="21" t="s">
         <v>7</v>
@@ -1988,10 +2074,12 @@
       <c r="B17" s="6">
         <v>0.54166666666666696</v>
       </c>
-      <c r="C17" s="7"/>
+      <c r="C17" s="7" t="s">
+        <v>37</v>
+      </c>
       <c r="D17" s="7"/>
-      <c r="E17" s="40" t="s">
-        <v>37</v>
+      <c r="E17" s="37" t="s">
+        <v>34</v>
       </c>
       <c r="F17" s="22"/>
     </row>
@@ -1999,25 +2087,27 @@
       <c r="B18" s="6">
         <v>0.58333333333333304</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="E18" s="40" t="s">
-        <v>38</v>
+      <c r="C18" s="7"/>
+      <c r="D18" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="37" t="s">
+        <v>35</v>
       </c>
       <c r="F18" s="22"/>
     </row>
-    <row r="19" spans="2:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" ht="66" x14ac:dyDescent="0.3">
       <c r="B19" s="6">
         <v>0.625</v>
       </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="40" t="s">
-        <v>39</v>
+      <c r="C19" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="37" t="s">
+        <v>36</v>
       </c>
       <c r="F19" s="21" t="s">
         <v>8</v>
@@ -2027,33 +2117,35 @@
       <c r="B20" s="6">
         <v>0.66666666666666696</v>
       </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="40" t="s">
-        <v>35</v>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="37" t="s">
+        <v>32</v>
       </c>
       <c r="F20" s="7"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" ht="33" x14ac:dyDescent="0.3">
       <c r="B21" s="6">
         <v>0.70833333333333304</v>
       </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="40"/>
+      <c r="C21" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="40"/>
+      <c r="E21" s="37"/>
       <c r="F21" s="7"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" ht="33" x14ac:dyDescent="0.3">
       <c r="B22" s="6">
         <v>0.75</v>
       </c>
-      <c r="C22" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22" s="40"/>
+      <c r="C22" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="E22" s="37"/>
       <c r="F22" s="7"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
@@ -2062,27 +2154,29 @@
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
-      <c r="E23" s="40"/>
+      <c r="E23" s="37"/>
       <c r="F23" s="7"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6" ht="33" x14ac:dyDescent="0.3">
       <c r="B24" s="6">
         <v>0.83333333333333304</v>
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
-      <c r="E24" s="40" t="s">
+      <c r="E24" s="38" t="s">
         <v>40</v>
       </c>
       <c r="F24" s="7"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" ht="33" x14ac:dyDescent="0.3">
       <c r="B25" s="6">
         <v>0.875</v>
       </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="48" t="s">
+        <v>51</v>
+      </c>
       <c r="F25" s="7"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.3">
@@ -2091,7 +2185,7 @@
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
+      <c r="E26" s="40"/>
       <c r="F26" s="7"/>
     </row>
     <row r="27" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2107,11 +2201,11 @@
       <c r="B28" s="23">
         <v>1</v>
       </c>
-      <c r="C28" s="43" t="s">
+      <c r="C28" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="D28" s="44"/>
-      <c r="E28" s="45"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="43"/>
       <c r="F28" s="17"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.3">
@@ -2148,15 +2242,15 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L23" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -2183,16 +2277,16 @@
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" s="28"/>
       <c r="C2" s="28" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E2" s="8"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="29" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C3" s="29">
         <v>1</v>
@@ -2204,7 +2298,7 @@
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" s="30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C4" s="31">
         <f>681900*2</f>
@@ -2215,7 +2309,7 @@
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" s="30" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C5" s="31">
         <v>472602</v>
@@ -2225,7 +2319,7 @@
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" s="30" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C6" s="31">
         <f>57000*2</f>
@@ -2235,19 +2329,29 @@
       <c r="E6" s="32"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="30"/>
-      <c r="C7" s="31"/>
+      <c r="B7" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="31">
+        <f>2270+2520</f>
+        <v>4790</v>
+      </c>
       <c r="D7" s="31"/>
       <c r="E7" s="32"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="33"/>
-      <c r="C8" s="31"/>
+      <c r="B8" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="31">
+        <f>2700+2950</f>
+        <v>5650</v>
+      </c>
       <c r="D8" s="31"/>
       <c r="E8" s="32"/>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="34"/>
+      <c r="B9" s="30"/>
       <c r="C9" s="31"/>
       <c r="D9" s="31"/>
       <c r="E9" s="32"/>
@@ -2259,13 +2363,13 @@
       <c r="E10" s="32"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="34"/>
+      <c r="B11" s="30"/>
       <c r="C11" s="31"/>
       <c r="D11" s="31"/>
       <c r="E11" s="32"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="33"/>
+      <c r="B12" s="30"/>
       <c r="C12" s="31"/>
       <c r="D12" s="31"/>
       <c r="E12" s="32"/>
@@ -2631,26 +2735,26 @@
       <c r="E72" s="32"/>
     </row>
     <row r="73" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="35"/>
-      <c r="C73" s="36"/>
-      <c r="D73" s="36"/>
+      <c r="B73" s="30"/>
+      <c r="C73" s="33"/>
+      <c r="D73" s="33"/>
       <c r="E73" s="32"/>
     </row>
     <row r="74" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="C74" s="38">
+      <c r="B74" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="C74" s="35">
         <f>SUM(C4:C73)*C3</f>
-        <v>1950402</v>
-      </c>
-      <c r="D74" s="38">
+        <v>1960842</v>
+      </c>
+      <c r="D74" s="35">
         <f>SUM(D4:D73)*D3</f>
         <v>0</v>
       </c>
-      <c r="E74" s="39">
+      <c r="E74" s="36">
         <f>SUM(C74:D74)</f>
-        <v>1950402</v>
+        <v>1960842</v>
       </c>
     </row>
   </sheetData>
